--- a/Result/profitability/4744.xlsx
+++ b/Result/profitability/4744.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM56"/>
+  <dimension ref="A1:AM57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>3.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7925000000000001</v>
+        <v>0.8137500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>43.5975</v>
+        <v>46.05125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>5.06</v>
       </c>
       <c r="M3" t="n">
-        <v>1.46625</v>
+        <v>1.3125</v>
       </c>
       <c r="N3" t="n">
-        <v>42.23625</v>
+        <v>44.88</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.82</v>
       </c>
       <c r="M4" t="n">
-        <v>1.435</v>
+        <v>1.37875</v>
       </c>
       <c r="N4" t="n">
-        <v>41.105</v>
+        <v>42.77875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>1.67375</v>
+        <v>1.61125</v>
       </c>
       <c r="N5" t="n">
-        <v>39.6925</v>
+        <v>42.28625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>1.66</v>
+        <v>1.595</v>
       </c>
       <c r="N6" t="n">
-        <v>39.5675</v>
+        <v>41.64375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5925</v>
+        <v>1.3825</v>
       </c>
       <c r="N7" t="n">
-        <v>39.08374999999999</v>
+        <v>41.61875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -7540,6 +7540,133 @@
       </c>
       <c r="AM56" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4744</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>191</v>
+      </c>
+      <c r="D57" t="n">
+        <v>71</v>
+      </c>
+      <c r="E57" t="n">
+        <v>120</v>
+      </c>
+      <c r="F57" t="n">
+        <v>62.71</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-6.11%</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.3725000000000001</v>
+      </c>
+      <c r="N57" t="n">
+        <v>46.35875</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W57" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0.4545454545454546</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.4346831388698238</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>-1.470588235294118</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.4945185891325072</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK57" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
